--- a/开发相关/气缸电压和压力映射_20250918.xlsx
+++ b/开发相关/气缸电压和压力映射_20250918.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\wanxiang\EPBTest\开发相关\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5FF5D11-122B-4EC7-8EBF-0149D85C7149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883A68C5-DC33-437A-96E1-4FADEB162707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="6204" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,18 +17,41 @@
     <sheet name="气缸2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
   <si>
     <t>电压</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>压力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置电压</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预期压力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>应设置电压</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2089,16 +2112,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>340570</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>32384</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>249130</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>105726</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>390524</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>121395</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>299083</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>24237</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2127,8 +2150,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5461210" y="382904"/>
-          <a:ext cx="4528610" cy="4298109"/>
+          <a:off x="6009850" y="105726"/>
+          <a:ext cx="4528609" cy="4300966"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2517,103 +2540,165 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="11.796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>31.658999999999999</v>
       </c>
+      <c r="D2">
+        <v>3.2</v>
+      </c>
+      <c r="E2">
+        <f>D2*39.101-7.886</f>
+        <v>117.2372</v>
+      </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1.5</v>
       </c>
       <c r="B3">
         <v>49.936999999999998</v>
       </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E12" si="0">D3*39.101-7.886</f>
+        <v>-7.8860000000000001</v>
+      </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4">
         <v>70.165999999999997</v>
       </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>-7.8860000000000001</v>
+      </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2.5</v>
       </c>
       <c r="B5">
         <v>90.194000000000003</v>
       </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>-7.8860000000000001</v>
+      </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6">
         <v>109.84</v>
       </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>-7.8860000000000001</v>
+      </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>3.5</v>
       </c>
       <c r="B7">
         <v>128.86000000000001</v>
       </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>-7.8860000000000001</v>
+      </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>4</v>
       </c>
       <c r="B8">
         <v>148.44999999999999</v>
       </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>-7.8860000000000001</v>
+      </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>4.5</v>
       </c>
       <c r="B9">
         <v>167.97</v>
       </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>-7.8860000000000001</v>
+      </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>5</v>
       </c>
       <c r="B10">
         <v>188.04</v>
       </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>-7.8860000000000001</v>
+      </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>5.5</v>
       </c>
       <c r="B11">
         <v>206.76</v>
       </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>-7.8860000000000001</v>
+      </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>6</v>
       </c>
       <c r="B12">
         <v>226.75</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>-7.8860000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/开发相关/气缸电压和压力映射_20250918.xlsx
+++ b/开发相关/气缸电压和压力映射_20250918.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\wanxiang\EPBTest\开发相关\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883A68C5-DC33-437A-96E1-4FADEB162707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2A2185-0CAA-4411-AF05-FA60A8C25458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="6204" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2112,16 +2112,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>249130</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>105726</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>336760</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>54291</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>299083</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>24237</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>174305</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>145204</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2150,8 +2150,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6009850" y="105726"/>
-          <a:ext cx="4528609" cy="4300966"/>
+          <a:off x="4817320" y="755331"/>
+          <a:ext cx="4523845" cy="4297153"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
